--- a/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
@@ -490,19 +490,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-2 熱量與比熱　測驗　★☆☆ 基礎（記憶・理解）</t>
+          <t>國二上學期 八上5-2 熱量與比熱　測驗　★☆☆ 基礎（記憶・理解）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -519,16 +523,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -537,18 +561,38 @@
           <t>熱由何處流向何處？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>比熱大</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>高溫流向低溫</t>
         </is>
       </c>
-      <c r="D3" s="4" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>熱流</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -557,18 +601,38 @@
           <t>熱量常用單位是？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>卡(cal)</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>高溫流向低溫</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>熱能</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -577,18 +641,38 @@
           <t>使1克物質升1℃所需熱量是？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>比熱大</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>比熱</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -597,18 +681,38 @@
           <t>水的比熱是多少？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>比熱小且導熱快帶走體熱</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
+          <t>油(比熱較小)</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>1 cal/g℃</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>較大</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -617,18 +721,38 @@
           <t>比熱是物質的什麼？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
         <is>
           <t>特性</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
+          <t>比熱</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>熱量</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
+        <is>
           <t>可辨別</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -637,18 +761,38 @@
           <t>熱是一種？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>比熱</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>比熱大</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>能量</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>非物質</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -657,18 +801,38 @@
           <t>比熱大的物質升溫？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
         <is>
           <t>慢</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>不易升溫</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -677,18 +841,38 @@
           <t>兩物達熱平衡時溫度？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>熱量</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>相同</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>停止流動</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -697,18 +881,38 @@
           <t>熱量的常用單位是？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
         <is>
           <t>卡(cal)</t>
         </is>
       </c>
-      <c r="D11" s="4" t="inlineStr">
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>比熱</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
         <is>
           <t>熱量</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -717,12 +921,32 @@
           <t>比熱越大的物質溫度越？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>難改變</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>比熱</t>
         </is>
@@ -730,7 +954,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -742,19 +966,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-2 熱量與比熱　測驗　★★☆ 進階（應用・分析）</t>
+          <t>國二上學期 八上5-2 熱量與比熱　測驗　★★☆ 進階（應用・分析）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -771,16 +999,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -789,18 +1037,38 @@
           <t>水與鐵誰升溫較快？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>鐵</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>快</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>熱量</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>比熱小</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -809,18 +1077,38 @@
           <t>海邊溫差小是因為水的？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>比熱大</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>比熱</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>調節</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -829,18 +1117,38 @@
           <t>比熱小的金屬降溫？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>慢</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>快</t>
         </is>
       </c>
-      <c r="D5" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
         <is>
           <t>易散熱</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -849,18 +1157,38 @@
           <t>熱量多寡與哪些有關？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
         <is>
           <t>質量比熱溫度變化</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
         <is>
+          <t>1 cal/g℃</t>
+        </is>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>水比熱大能吸多熱</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
+        <is>
           <t>三者</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -869,18 +1197,38 @@
           <t>同質量水與油加熱誰快升溫？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>油(比熱較小)</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>海陸升降溫速率不同造成氣壓差</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>較快</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -889,18 +1237,38 @@
           <t>暖暖包提供的是？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>比熱大</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>比熱</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>熱量</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>水</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>放熱</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -909,18 +1277,38 @@
           <t>熱流動到何時停止？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>比熱小且導熱快帶走體熱</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
         <is>
           <t>熱平衡(同溫)</t>
         </is>
       </c>
-      <c r="D9" s="4" t="inlineStr">
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>水比熱大能吸多熱</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
         <is>
           <t>終止</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -929,18 +1317,38 @@
           <t>鐵鍋比陶鍋快熱因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>較大</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>比熱小</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>升溫快</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -949,18 +1357,38 @@
           <t>比熱大的水適合當？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>冷卻劑或暖氣介質</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>油(比熱較小)</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>熱量還取決質量與比熱</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -969,12 +1397,32 @@
           <t>相同質量水與沙誰比熱大？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
         <is>
           <t>水</t>
         </is>
       </c>
       <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>鐵</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>熱量</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
+        <is>
+          <t>相同</t>
+        </is>
+      </c>
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>比熱</t>
         </is>
@@ -982,7 +1430,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -994,19 +1442,23 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="62" customWidth="1" min="2" max="2"/>
+    <col width="54" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="42" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="8" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>國二上學期 八上5-2 熱量與比熱　測驗　★★★ 挑戰（評鑑・創造）</t>
+          <t>國二上學期 八上5-2 熱量與比熱　測驗　★★★ 挑戰（評鑑・創造）（四選一單選）</t>
         </is>
       </c>
     </row>
@@ -1023,16 +1475,36 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>(A)</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>(B)</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>(C)</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>(D)</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
           <t>答案</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>解析</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="34" customHeight="1">
+    <row r="3" ht="40" customHeight="1">
       <c r="A3" s="3" t="n">
         <v>1</v>
       </c>
@@ -1041,18 +1513,38 @@
           <t>為何溫度高不代表熱量多？</t>
         </is>
       </c>
-      <c r="C3" s="5" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>熱量還取決質量與比熱</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>水比熱大能吸多熱</t>
+        </is>
+      </c>
+      <c r="G3" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H3" s="4" t="inlineStr">
+        <is>
           <t>綜合</t>
         </is>
       </c>
     </row>
-    <row r="4" ht="34" customHeight="1">
+    <row r="4" ht="40" customHeight="1">
       <c r="A4" s="6" t="n">
         <v>2</v>
       </c>
@@ -1061,18 +1553,38 @@
           <t>沙灘白天燙腳海水卻涼因為？</t>
         </is>
       </c>
-      <c r="C4" s="8" t="inlineStr">
+      <c r="C4" s="7" t="inlineStr">
         <is>
           <t>沙比熱小升溫快、水比熱大</t>
         </is>
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
+          <t>1 cal/g℃</t>
+        </is>
+      </c>
+      <c r="E4" s="7" t="inlineStr">
+        <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="F4" s="7" t="inlineStr">
+        <is>
+          <t>油(比熱較小)</t>
+        </is>
+      </c>
+      <c r="G4" s="8" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H4" s="7" t="inlineStr">
+        <is>
           <t>比熱差</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="34" customHeight="1">
+    <row r="5" ht="40" customHeight="1">
       <c r="A5" s="3" t="n">
         <v>3</v>
       </c>
@@ -1081,18 +1593,38 @@
           <t>相同熱量給水和鐵誰升溫多？</t>
         </is>
       </c>
-      <c r="C5" s="5" t="inlineStr">
+      <c r="C5" s="4" t="inlineStr">
         <is>
           <t>鐵</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
+          <t>比熱大</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>能量</t>
+        </is>
+      </c>
+      <c r="F5" s="4" t="inlineStr">
+        <is>
+          <t>高溫流向低溫</t>
+        </is>
+      </c>
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H5" s="4" t="inlineStr">
+        <is>
           <t>比熱小升溫多</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="34" customHeight="1">
+    <row r="6" ht="40" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>4</v>
       </c>
@@ -1101,18 +1633,38 @@
           <t>冷卻電腦為何用水？</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>海陸升降溫速率不同造成氣壓差</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
         <is>
           <t>水比熱大能吸多熱</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>熱量還取決質量與比熱</t>
+        </is>
+      </c>
+      <c r="F6" s="7" t="inlineStr">
+        <is>
+          <t>缺乏大量水調節</t>
+        </is>
+      </c>
+      <c r="G6" s="8" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>散熱</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="34" customHeight="1">
+    <row r="7" ht="40" customHeight="1">
       <c r="A7" s="3" t="n">
         <v>5</v>
       </c>
@@ -1121,18 +1673,38 @@
           <t>高溫小鐵塊與低溫大水盆接觸最終？</t>
         </is>
       </c>
-      <c r="C7" s="5" t="inlineStr">
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
         <is>
           <t>趨同溫,水盆變化小</t>
         </is>
       </c>
-      <c r="D7" s="4" t="inlineStr">
+      <c r="E7" s="4" t="inlineStr">
+        <is>
+          <t>油(比熱較小)</t>
+        </is>
+      </c>
+      <c r="F7" s="4" t="inlineStr">
+        <is>
+          <t>沙比熱小升溫快、水比熱大</t>
+        </is>
+      </c>
+      <c r="G7" s="5" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="H7" s="4" t="inlineStr">
         <is>
           <t>熱平衡</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="34" customHeight="1">
+    <row r="8" ht="40" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>6</v>
       </c>
@@ -1141,18 +1713,38 @@
           <t>比熱概念如何解釋日夜海陸風？</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>比熱小且導熱快帶走體熱</t>
+        </is>
+      </c>
+      <c r="D8" s="7" t="inlineStr">
+        <is>
+          <t>1 cal/g℃</t>
+        </is>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
         <is>
           <t>海陸升降溫速率不同造成氣壓差</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
+        <is>
+          <t>熱平衡(同溫)</t>
+        </is>
+      </c>
+      <c r="G8" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H8" s="7" t="inlineStr">
         <is>
           <t>應用</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="40" customHeight="1">
       <c r="A9" s="3" t="n">
         <v>7</v>
       </c>
@@ -1161,18 +1753,38 @@
           <t>為何內陸日夜溫差大？</t>
         </is>
       </c>
-      <c r="C9" s="5" t="inlineStr">
+      <c r="C9" s="4" t="inlineStr">
         <is>
           <t>缺乏大量水調節</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
+          <t>熱平衡(同溫)</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>1 cal/g℃</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>沙比熱小升溫快、水比熱大</t>
+        </is>
+      </c>
+      <c r="G9" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
           <t>比熱</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="34" customHeight="1">
+    <row r="10" ht="40" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>8</v>
       </c>
@@ -1181,18 +1793,38 @@
           <t>金屬摸起來較涼因為？</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>熱量還取決質量與比熱</t>
+        </is>
+      </c>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>質量比熱溫度變化</t>
+        </is>
+      </c>
+      <c r="E10" s="7" t="inlineStr">
         <is>
           <t>比熱小且導熱快帶走體熱</t>
         </is>
       </c>
-      <c r="D10" s="7" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
+        <is>
+          <t>熱平衡(同溫)</t>
+        </is>
+      </c>
+      <c r="G10" s="8" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="H10" s="7" t="inlineStr">
         <is>
           <t>觸感</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="34" customHeight="1">
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="3" t="n">
         <v>9</v>
       </c>
@@ -1201,18 +1833,38 @@
           <t>為何沿海地區日夜溫差比內陸小？</t>
         </is>
       </c>
-      <c r="C11" s="5" t="inlineStr">
+      <c r="C11" s="4" t="inlineStr">
         <is>
           <t>水比熱大調節溫度</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
+          <t>沙比熱小升溫快、水比熱大</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>熱量還取決質量與比熱</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>冷卻劑或暖氣介質</t>
+        </is>
+      </c>
+      <c r="G11" s="5" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
           <t>比熱</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="34" customHeight="1">
+    <row r="12" ht="40" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>10</v>
       </c>
@@ -1221,12 +1873,32 @@
           <t>相同熱量下比熱小的物質溫度變化？</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>卡(cal)</t>
+        </is>
+      </c>
+      <c r="D12" s="7" t="inlineStr">
+        <is>
+          <t>熱量</t>
+        </is>
+      </c>
+      <c r="E12" s="7" t="inlineStr">
+        <is>
+          <t>特性</t>
+        </is>
+      </c>
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>較大</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="G12" s="8" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="H12" s="7" t="inlineStr">
         <is>
           <t>反比</t>
         </is>
@@ -1234,7 +1906,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
-          <t>比熱小且導熱快帶走體熱</t>
+          <t>比熱小,微量吸熱溫度變化就大</t>
         </is>
       </c>
       <c r="D6" s="7" t="inlineStr">
@@ -1279,7 +1279,7 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>比熱小且導熱快帶走體熱</t>
+          <t>比熱小,微量吸熱溫度變化就大</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
@@ -1715,7 +1715,7 @@
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>比熱小且導熱快帶走體熱</t>
+          <t>比熱小,微量吸熱溫度變化就大</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>比熱小且導熱快帶走體熱</t>
+          <t>比熱小,微量吸熱溫度變化就大</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">

--- a/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
@@ -588,7 +588,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>熱流</t>
+          <t>熱流：熱量會自然地從溫度較高的地方流向溫度較低的地方，直到達到熱平衡</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>熱能</t>
+          <t>熱能：熱量常用的單位是卡(cal)，定義是使1公克水溫度上升1℃所需的熱量</t>
         </is>
       </c>
     </row>
@@ -668,7 +668,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>特性</t>
+          <t>特性：使1公克某物質溫度上升1℃所需要的熱量，稱為該物質的比熱，是物質固有的特性</t>
         </is>
       </c>
     </row>
@@ -708,7 +708,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>較大</t>
+          <t>較大：水的比熱是1卡/公克℃，和其他常見物質相比屬於比較大的比熱值</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>可辨別</t>
+          <t>可辨別：比熱是每種物質固有的特性數值，可以幫助辨別或區分不同物質</t>
         </is>
       </c>
     </row>
@@ -788,7 +788,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>非物質</t>
+          <t>非物質：熱是一種能量的形式，會在物體之間傳遞，本身不是實體物質</t>
         </is>
       </c>
     </row>
@@ -828,7 +828,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>不易升溫</t>
+          <t>不易升溫：比熱越大的物質，吸收相同熱量時溫度上升的幅度越小，所以升溫比較慢</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>停止流動</t>
+          <t>停止流動：兩物體達到熱平衡狀態時，彼此之間不再有淨熱量流動，此時兩者的溫度相同</t>
         </is>
       </c>
     </row>
@@ -908,7 +908,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>熱量</t>
+          <t>熱量：熱量常用的單位是卡(cal)，定義是使1公克水溫度上升1℃所需的熱量</t>
         </is>
       </c>
     </row>
@@ -948,7 +948,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>比熱</t>
+          <t>比熱：比熱越大的物質，吸收或放出相同熱量時溫度變化越小，也就是溫度越不容易改變</t>
         </is>
       </c>
     </row>
@@ -1064,7 +1064,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>比熱小</t>
+          <t>比熱小：鐵的比熱比水小很多，吸收相同熱量時溫度變化較大，所以升溫比水快</t>
         </is>
       </c>
     </row>
@@ -1104,7 +1104,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>調節</t>
+          <t>調節：海水比熱很大，白天吸熱不容易快速升溫、夜間放熱也不容易快速降溫，能有效調節沿海地區的氣溫，使日夜溫差較小</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>易散熱</t>
+          <t>易散熱：比熱小的物質，放出少量熱量溫度就會明顯下降，所以降溫速度較快</t>
         </is>
       </c>
     </row>
@@ -1184,7 +1184,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>三者</t>
+          <t>三者：物體吸收或放出的熱量多寡，和物體的質量、比熱、以及溫度變化量這三個因素都有關係</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>較快</t>
+          <t>較快：油的比熱比水小，相同質量下吸收相同熱量時，油的溫度上升幅度比水大，所以升溫較快</t>
         </is>
       </c>
     </row>
@@ -1264,7 +1264,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>放熱</t>
+          <t>放熱：暖暖包內的化學物質發生放熱反應，持續釋放出熱量，讓人感覺溫暖</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>終止</t>
+          <t>終止：熱量會持續從高溫處流向低溫處，直到兩者溫度相同、達到熱平衡狀態，熱的淨流動才會停止</t>
         </is>
       </c>
     </row>
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>升溫快</t>
+          <t>升溫快：鐵的比熱比陶瓷小，吸收相同熱量時溫度上升較快，所以鐵鍋比陶鍋更快變熱</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：水的比熱很大，能吸收大量熱量而溫度變化不大，很適合用來當冷卻劑或暖氣系統中傳遞熱量的介質</t>
         </is>
       </c>
     </row>
@@ -1424,7 +1424,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>比熱</t>
+          <t>比熱：水的比熱遠大於沙，相同質量下，水需要吸收更多熱量才能使溫度上升相同幅度</t>
         </is>
       </c>
     </row>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>綜合</t>
+          <t>綜合：熱量的多寡不只看溫度，還要考慮物體的質量和比熱，質量小或比熱小的物體即使溫度很高，含有的熱量也可能比質量大、比熱大的物體少</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="H4" s="7" t="inlineStr">
         <is>
-          <t>比熱差</t>
+          <t>比熱差：沙的比熱比水小很多，白天受到陽光照射後溫度快速升高、燙腳；海水比熱大，吸收同樣的太陽能溫度上升幅度小，所以摸起來仍然涼涼的</t>
         </is>
       </c>
     </row>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>比熱小升溫多</t>
+          <t>比熱小升溫多：鐵的比熱比水小，相同質量下吸收相同熱量時，比熱小的鐵溫度上升幅度比水大</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="H6" s="7" t="inlineStr">
         <is>
-          <t>散熱</t>
+          <t>散熱：水的比熱很大，能吸收大量熱量而溫度變化不大，很適合用來當作水冷系統的冷卻介質，有效把電腦產生的熱帶走</t>
         </is>
       </c>
     </row>
@@ -1700,7 +1700,7 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>熱平衡</t>
+          <t>熱平衡：兩者接觸後熱量會從高溫的鐵塊流向低溫的水盆，最終達到相同溫度；因為水盆質量大、比熱又大，能吸收的熱量遠超過小鐵塊放出的熱量，所以水盆整體溫度變化很小，最終溫度會比較接近水盆原本的溫度</t>
         </is>
       </c>
     </row>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="H8" s="7" t="inlineStr">
         <is>
-          <t>應用</t>
+          <t>應用：陸地比熱小，白天升溫快、夜晚降溫也快；海洋比熱大，升降溫都比較緩慢。這種升降溫速率的差異造成海陸之間的氣壓差，進而形成白天吹海風、夜晚吹陸風的現象</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>比熱</t>
+          <t>比熱：內陸地區遠離海洋，缺乏比熱大的大量水體來調節溫度，白天升溫快、夜晚降溫也快，所以日夜溫差比沿海地區大</t>
         </is>
       </c>
     </row>
@@ -1820,7 +1820,7 @@
       </c>
       <c r="H10" s="7" t="inlineStr">
         <is>
-          <t>觸感</t>
+          <t>觸感：金屬的比熱小，手接觸時只要吸收(或流失)一點點熱量，溫度就會有明顯變化，這種快速的溫度變化讓人感覺比較涼</t>
         </is>
       </c>
     </row>
@@ -1860,7 +1860,7 @@
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>比熱</t>
+          <t>比熱：海水比熱很大，白天吸熱不容易快速升溫、夜間放熱也不容易快速降溫，能有效調節沿海地區的氣溫，使日夜溫差比遠離海洋的內陸地區小</t>
         </is>
       </c>
     </row>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="H12" s="7" t="inlineStr">
         <is>
-          <t>反比</t>
+          <t>反比：比熱和溫度變化成反比，在吸收相同熱量的情況下，比熱越小的物質溫度上升(或下降)的幅度越大</t>
         </is>
       </c>
     </row>

--- a/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
+++ b/02_加值成品/八上/八上5-2_三種難度測驗卷.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>比熱大</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>快</t>
+          <t>能量</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
@@ -1084,17 +1084,17 @@
       </c>
       <c r="D4" s="7" t="inlineStr">
         <is>
-          <t>卡(cal)</t>
+          <t>相同</t>
         </is>
       </c>
       <c r="E4" s="7" t="inlineStr">
         <is>
-          <t>比熱</t>
+          <t>慢</t>
         </is>
       </c>
       <c r="F4" s="7" t="inlineStr">
         <is>
-          <t>鐵</t>
+          <t>熱量</t>
         </is>
       </c>
       <c r="G4" s="8" t="inlineStr">
@@ -1319,17 +1319,17 @@
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>較大</t>
+          <t>高溫流向低溫</t>
         </is>
       </c>
       <c r="D10" s="7" t="inlineStr">
         <is>
-          <t>能量</t>
+          <t>熱量</t>
         </is>
       </c>
       <c r="E10" s="7" t="inlineStr">
         <is>
-          <t>鐵</t>
+          <t>快</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
